--- a/research/traditional_assets/database/data/kenya/kenya_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_r_e_i_t.xlsx
@@ -588,40 +588,40 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.3292418772563177</v>
+        <v>0.4296296296296296</v>
       </c>
       <c r="H2">
-        <v>0.3292418772563177</v>
+        <v>0.4296296296296296</v>
       </c>
       <c r="I2">
-        <v>0.4476534296028881</v>
+        <v>0.3740740740740741</v>
       </c>
       <c r="J2">
-        <v>0.4476534296028881</v>
+        <v>0.3740740740740741</v>
       </c>
       <c r="K2">
-        <v>-0.678</v>
+        <v>-0.203</v>
       </c>
       <c r="L2">
-        <v>-0.2447653429602888</v>
+        <v>-0.07518518518518519</v>
       </c>
       <c r="M2">
-        <v>0.767</v>
+        <v>0.836</v>
       </c>
       <c r="N2">
-        <v>0.08023012552301255</v>
+        <v>0.1145205479452055</v>
       </c>
       <c r="O2">
-        <v>-1.131268436578171</v>
+        <v>-4.118226600985222</v>
       </c>
       <c r="P2">
-        <v>0.767</v>
+        <v>0.836</v>
       </c>
       <c r="Q2">
-        <v>0.08023012552301255</v>
+        <v>0.1145205479452055</v>
       </c>
       <c r="R2">
-        <v>-1.131268436578171</v>
+        <v>-4.118226600985222</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,31 +630,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.33</v>
+        <v>0.875</v>
       </c>
       <c r="V2">
-        <v>0.03451882845188285</v>
+        <v>0.1198630136986301</v>
       </c>
       <c r="W2">
-        <v>-0.0197093023255814</v>
+        <v>-0.006766666666666667</v>
       </c>
       <c r="X2">
-        <v>0.1177970215990332</v>
+        <v>0.1095679049993439</v>
       </c>
       <c r="Y2">
-        <v>-0.1375063239246146</v>
+        <v>-0.1163345716660106</v>
       </c>
       <c r="Z2">
-        <v>0.08310831083108311</v>
+        <v>0.09100101112234581</v>
       </c>
       <c r="AA2">
-        <v>0.0372037203720372</v>
+        <v>0.03404111897539602</v>
       </c>
       <c r="AB2">
-        <v>0.1177970215990332</v>
+        <v>0.1095679049993439</v>
       </c>
       <c r="AC2">
-        <v>-0.08059330122699601</v>
+        <v>-0.07552678602394787</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.33</v>
+        <v>-0.875</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.03575297941495124</v>
+        <v>-0.1361867704280156</v>
       </c>
       <c r="AK2">
-        <v>-0.01112234580384226</v>
+        <v>-0.03767491926803014</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.264</v>
+        <v>-0.8578431372549019</v>
       </c>
     </row>
     <row r="3">
@@ -710,40 +710,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.3292418772563177</v>
+        <v>0.4296296296296296</v>
       </c>
       <c r="H3">
-        <v>0.3292418772563177</v>
+        <v>0.4296296296296296</v>
       </c>
       <c r="I3">
-        <v>0.4476534296028881</v>
+        <v>0.3740740740740741</v>
       </c>
       <c r="J3">
-        <v>0.4476534296028881</v>
+        <v>0.3740740740740741</v>
       </c>
       <c r="K3">
-        <v>-0.678</v>
+        <v>-0.203</v>
       </c>
       <c r="L3">
-        <v>-0.2447653429602888</v>
+        <v>-0.07518518518518519</v>
       </c>
       <c r="M3">
-        <v>0.767</v>
+        <v>0.836</v>
       </c>
       <c r="N3">
-        <v>0.08023012552301255</v>
+        <v>0.1145205479452055</v>
       </c>
       <c r="O3">
-        <v>-1.131268436578171</v>
+        <v>-4.118226600985222</v>
       </c>
       <c r="P3">
-        <v>0.767</v>
+        <v>0.836</v>
       </c>
       <c r="Q3">
-        <v>0.08023012552301255</v>
+        <v>0.1145205479452055</v>
       </c>
       <c r="R3">
-        <v>-1.131268436578171</v>
+        <v>-4.118226600985222</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -752,31 +752,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.33</v>
+        <v>0.875</v>
       </c>
       <c r="V3">
-        <v>0.03451882845188285</v>
+        <v>0.1198630136986301</v>
       </c>
       <c r="W3">
-        <v>-0.0197093023255814</v>
+        <v>-0.006766666666666667</v>
       </c>
       <c r="X3">
-        <v>0.1177970215990332</v>
+        <v>0.1095679049993439</v>
       </c>
       <c r="Y3">
-        <v>-0.1375063239246146</v>
+        <v>-0.1163345716660106</v>
       </c>
       <c r="Z3">
-        <v>0.08310831083108311</v>
+        <v>0.09100101112234581</v>
       </c>
       <c r="AA3">
-        <v>0.0372037203720372</v>
+        <v>0.03404111897539602</v>
       </c>
       <c r="AB3">
-        <v>0.1177970215990332</v>
+        <v>0.1095679049993439</v>
       </c>
       <c r="AC3">
-        <v>-0.08059330122699601</v>
+        <v>-0.07552678602394787</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.33</v>
+        <v>-0.875</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -797,10 +797,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.03575297941495124</v>
+        <v>-0.1361867704280156</v>
       </c>
       <c r="AK3">
-        <v>-0.01112234580384226</v>
+        <v>-0.03767491926803014</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.264</v>
+        <v>-0.8578431372549019</v>
       </c>
     </row>
   </sheetData>
